--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113275270</v>
       </c>
       <c r="B2" t="n">
-        <v>104364</v>
+        <v>104380</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113275270</v>
       </c>
       <c r="B2" t="n">
-        <v>104380</v>
+        <v>104394</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113275270</v>
       </c>
       <c r="B2" t="n">
-        <v>104394</v>
+        <v>104416</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113275270</v>
       </c>
       <c r="B2" t="n">
-        <v>104416</v>
+        <v>104420</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>113275270</v>
       </c>
       <c r="B2" t="n">
-        <v>104420</v>
+        <v>104426</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,6 +785,238 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113587838</v>
+      </c>
+      <c r="B3" t="n">
+        <v>74283</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hökenäs, Dalarne, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>345996</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6561087</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113587824</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90053</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hökenäs, Dalarne, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>345957</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6561200</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grankvist, levande stående gran</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113587838</v>
+        <v>113587824</v>
       </c>
       <c r="B3" t="n">
-        <v>74283</v>
+        <v>90053</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345996</v>
+        <v>345957</v>
       </c>
       <c r="R3" t="n">
-        <v>6561087</v>
+        <v>6561200</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,6 +867,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På grankvist, levande stående gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,21 +883,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113587824</v>
+        <v>113587838</v>
       </c>
       <c r="B4" t="n">
-        <v>90053</v>
+        <v>74283</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345957</v>
+        <v>345996</v>
       </c>
       <c r="R4" t="n">
-        <v>6561200</v>
+        <v>6561087</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,11 +978,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-12-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grankvist, levande stående gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,6 +989,21 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113275270</v>
       </c>
       <c r="B2" t="n">
-        <v>104426</v>
+        <v>104433</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>113587824</v>
       </c>
       <c r="B3" t="n">
-        <v>90053</v>
+        <v>90060</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>113587838</v>
       </c>
       <c r="B4" t="n">
-        <v>74283</v>
+        <v>74290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113587824</v>
+        <v>113587838</v>
       </c>
       <c r="B3" t="n">
-        <v>90060</v>
+        <v>74292</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345957</v>
+        <v>345996</v>
       </c>
       <c r="R3" t="n">
-        <v>6561200</v>
+        <v>6561087</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,11 +867,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-12-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På grankvist, levande stående gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,6 +878,21 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113587838</v>
+        <v>113587824</v>
       </c>
       <c r="B4" t="n">
-        <v>74290</v>
+        <v>90063</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345996</v>
+        <v>345957</v>
       </c>
       <c r="R4" t="n">
-        <v>6561087</v>
+        <v>6561200</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,6 +988,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grankvist, levande stående gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,21 +1004,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113587838</v>
+        <v>113587824</v>
       </c>
       <c r="B3" t="n">
-        <v>74292</v>
+        <v>90094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345996</v>
+        <v>345957</v>
       </c>
       <c r="R3" t="n">
-        <v>6561087</v>
+        <v>6561200</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,6 +867,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På grankvist, levande stående gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,21 +883,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113587824</v>
+        <v>113587838</v>
       </c>
       <c r="B4" t="n">
-        <v>90063</v>
+        <v>74320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345957</v>
+        <v>345996</v>
       </c>
       <c r="R4" t="n">
-        <v>6561200</v>
+        <v>6561087</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,11 +978,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-12-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grankvist, levande stående gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,6 +989,21 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113587824</v>
+        <v>113587838</v>
       </c>
       <c r="B3" t="n">
-        <v>90094</v>
+        <v>74320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345957</v>
+        <v>345996</v>
       </c>
       <c r="R3" t="n">
-        <v>6561200</v>
+        <v>6561087</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,11 +867,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-12-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På grankvist, levande stående gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,6 +878,21 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113587838</v>
+        <v>113587824</v>
       </c>
       <c r="B4" t="n">
-        <v>74320</v>
+        <v>90095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345996</v>
+        <v>345957</v>
       </c>
       <c r="R4" t="n">
-        <v>6561087</v>
+        <v>6561200</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,6 +988,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grankvist, levande stående gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,21 +1004,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113587838</v>
+        <v>113587824</v>
       </c>
       <c r="B3" t="n">
-        <v>74320</v>
+        <v>90099</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345996</v>
+        <v>345957</v>
       </c>
       <c r="R3" t="n">
-        <v>6561087</v>
+        <v>6561200</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,6 +867,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På grankvist, levande stående gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,21 +883,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113587824</v>
+        <v>113587838</v>
       </c>
       <c r="B4" t="n">
-        <v>90095</v>
+        <v>74320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345957</v>
+        <v>345996</v>
       </c>
       <c r="R4" t="n">
-        <v>6561200</v>
+        <v>6561087</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,11 +978,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-12-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grankvist, levande stående gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,6 +989,21 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113587824</v>
+        <v>113587838</v>
       </c>
       <c r="B3" t="n">
-        <v>90099</v>
+        <v>74320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345957</v>
+        <v>345996</v>
       </c>
       <c r="R3" t="n">
-        <v>6561200</v>
+        <v>6561087</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,11 +867,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-12-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På grankvist, levande stående gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,6 +878,21 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113587838</v>
+        <v>113587824</v>
       </c>
       <c r="B4" t="n">
-        <v>74320</v>
+        <v>90099</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345996</v>
+        <v>345957</v>
       </c>
       <c r="R4" t="n">
-        <v>6561087</v>
+        <v>6561200</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,6 +988,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grankvist, levande stående gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,21 +1004,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113587838</v>
+        <v>113587824</v>
       </c>
       <c r="B3" t="n">
-        <v>74320</v>
+        <v>90099</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345996</v>
+        <v>345957</v>
       </c>
       <c r="R3" t="n">
-        <v>6561087</v>
+        <v>6561200</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,6 +867,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På grankvist, levande stående gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,21 +883,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113587824</v>
+        <v>113587838</v>
       </c>
       <c r="B4" t="n">
-        <v>90099</v>
+        <v>74320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345957</v>
+        <v>345996</v>
       </c>
       <c r="R4" t="n">
-        <v>6561200</v>
+        <v>6561087</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,11 +978,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-12-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grankvist, levande stående gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,6 +989,21 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113275270</v>
+        <v>113587824</v>
       </c>
       <c r="B2" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalarne (Dalarne), Dls</t>
+          <t>Hökenäs, Dalarne, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346011</v>
+        <v>345957</v>
       </c>
       <c r="R2" t="n">
-        <v>6561125</v>
+        <v>6561199</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På grankvist, levande stående gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Roger Adolfsson, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -791,16 +784,11 @@
         <v>113587838</v>
       </c>
       <c r="B3" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -909,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113587824</v>
+        <v>113275270</v>
       </c>
       <c r="B4" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +908,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hökenäs, Dalarne, Dls</t>
+          <t>Dalarne, Dalarne, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345957</v>
+        <v>346011</v>
       </c>
       <c r="R4" t="n">
-        <v>6561199</v>
+        <v>6561125</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,17 +963,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-11-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grankvist, levande stående gran</t>
+          <t>2023-11-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +987,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1013,7 +998,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 53197-2023 artfynd.xlsx
+++ b/artfynd/A 53197-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113587824</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113587838</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,8 +1017,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113275270</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>